--- a/app/src/main/java/com/example/methodmesh/modules/spatialgeometry/docs/example_odk_spatialgeometry.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/spatialgeometry/docs/example_odk_spatialgeometry.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R9c1b51ec42984a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R2d7fd5d7c1d2477c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R19e0fd81e410448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R95f7c2425f784dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rcce8d01908b24780"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rcfb0267d363547fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -128,30 +128,12 @@
   <x:si>
     <x:t xml:space="preserve">Distance from angular size</x:t>
   </x:si>
-  <x:si>
-    <x:t xml:space="preserve">form_title</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">version</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">spatialgeometry</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">instance_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">uuid()</x:t>
-  </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -172,8 +154,13 @@
       <x:color rgb="FF332A27"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -185,6 +172,11 @@
         <x:fgColor rgb="FFE7D8D2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E8F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -192,7 +184,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -201,6 +193,20 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -632,32 +638,43 @@
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <x:cols>
     <x:col min="1" max="2" width="28" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15">
-      <x:c r="A1" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C1" s="3"/>
+      <x:c r="A1" s="8" t="str">
+        <x:v>form_title</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
+        <x:v>form_id</x:v>
+      </x:c>
+      <x:c r="C1" s="9" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="D1" s="11" t="str">
+        <x:v>instance_name</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="15">
-      <x:c r="A2" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>42</x:v>
+      <x:c r="A2" s="1" t="str">
+        <x:v>MethodMesh Spatial Geometry example</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="str">
+        <x:v>spatialgeometry_example</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>2026090702</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>uuid()</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15">
-      <x:c r="A3" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
